--- a/forms/trg/Formulir_TRG_ethno.xlsx
+++ b/forms/trg/Formulir_TRG_ethno.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B24)</f>
+        <f>COUNTA(Anggota!B5:B25)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F24)</f>
+        <f>COUNTA(Anggota!F5:F25)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,22 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Andi Muhammad Akhmar, S.S., M.Hum.</t>
+          <t>Prof. Dr. Fathu Rahman, M.Hum</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Cultural Studies, Bugis and Makassar Literature</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Literature</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,17 +937,17 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-5215-5205</t>
+          <t>0000-0001-9641-036X</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6024214</t>
+          <t>6027154</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57209507741</t>
+          <t>57205243994</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -962,17 +962,17 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. M. Dalyan, M.Hum.</t>
+          <t>Prof. Dr. Andi Muhammad Akhmar, S.S., M.Hum.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Linguistic Science</t>
+          <t>Cultural Studies, Bugis and Makassar Literature</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -986,17 +986,17 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-5385-9850</t>
+          <t>0000-0001-5215-5205</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6024211</t>
+          <t>6024214</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57709986400</t>
+          <t>57209507741</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1011,22 +1011,22 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Datuk Prof. Kolonel (K) Dr. Awang Azman Awang Pawi</t>
+          <t>Dr. M. Dalyan, M.Hum.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Malay Studie || scultural studies || postcolonial</t>
+          <t>Linguistic Science</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>University of Malaya</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1035,13 +1035,17 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-4939-2706</t>
-        </is>
-      </c>
-      <c r="K7" s="12" t="n"/>
+          <t>0000-0002-5385-9850</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>6024211</t>
+        </is>
+      </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>57192385082</t>
+          <t>57709986400</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1056,27 +1060,39 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Assoc. Prof. Dr. Aminoh Jehwae</t>
+          <t>Datuk Prof. Kolonel (K) Dr. Awang Azman Awang Pawi</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Prince of Songkla University</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="n"/>
+          <t>Malay Studie || scultural studies || postcolonial</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>University of Malaya</t>
+        </is>
+      </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-4939-2706</t>
+        </is>
+      </c>
       <c r="K8" s="12" t="n"/>
-      <c r="L8" s="12" t="n"/>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>57192385082</t>
+        </is>
+      </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1089,33 +1105,25 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Martina, M.Pd.</t>
+          <t>Assoc. Prof. Dr. Aminoh Jehwae</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>Research Center for Language, Literature, and Community BRIN RI</t>
-        </is>
-      </c>
+          <t>Prince of Songkla University</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="n"/>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>0009-0008-7911-9165</t>
-        </is>
-      </c>
+      <c r="J9" s="12" t="n"/>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="12" t="n"/>
       <c r="M9" s="11" t="inlineStr">
@@ -1130,25 +1138,33 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Hendrik I</t>
+          <t>Dr. Martina, M.Pd.</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="n"/>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Research Center for Language, Literature, and Community BRIN RI</t>
+        </is>
+      </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>0009-0008-7911-9165</t>
+        </is>
+      </c>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="12" t="n"/>
       <c r="M10" s="11" t="inlineStr">
@@ -1163,12 +1179,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Fakhreny Fathu Rahman</t>
+          <t>Hendrik I</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1196,12 +1212,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Ahmad Jaelani</t>
+          <t>Fakhreny Fathu Rahman</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1227,10 +1243,26 @@
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="11" t="n"/>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Ahmad Jaelani</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>The Ethno Literature Research Group is dedicated to preserving and advancing the cultural richness of Indonesia’s minority tribes through the study of literary heritage passed down across generations. By integrating the perspectives of ethnic literature and ethnographic literature, this group explores oral traditions such as folktales, pantun, expressions, advice, poems, proverbs, ancestral messages, songs, and mantras as meaningful reflections of identity, values, and collective memory. Our mission is to strengthen national culture by safeguarding the literary and cultural legacy of minority communities while promoting deeper academic understanding of their everyday lives, beliefs, and traditions.</t>
+        </is>
+      </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
@@ -1238,7 +1270,11 @@
       <c r="J13" s="12" t="n"/>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="12" t="n"/>
-      <c r="M13" s="12" t="n"/>
+      <c r="M13" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1427,15 +1463,32 @@
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="12" t="n"/>
     </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
